--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1045,6 +1045,125 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130292202</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57820</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stora Mölebo, SV dammen, S:t Sigfrid, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>562144</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6283682</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sankt Sigfrid</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lars Lidberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Lidberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130292202</v>
       </c>
       <c r="B5" t="n">
-        <v>57820</v>
+        <v>57846</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130292202</v>
       </c>
       <c r="B5" t="n">
-        <v>57846</v>
+        <v>57848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130292202</v>
       </c>
       <c r="B5" t="n">
-        <v>57848</v>
+        <v>57856</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130292202</v>
       </c>
       <c r="B5" t="n">
-        <v>57856</v>
+        <v>57857</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1050,7 +1050,7 @@
         <v>130292202</v>
       </c>
       <c r="B5" t="n">
-        <v>57857</v>
+        <v>57858</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1164,6 +1164,125 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133842236</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58243</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stora Mölebo, SV dammen, S:t Sigfrid, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>562144</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6283682</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nybro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sankt Sigfrid</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lars Lidberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lars Lidberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>133842236</v>
       </c>
       <c r="B6" t="n">
-        <v>58243</v>
+        <v>58250</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 13155-2025 artfynd.xlsx
+++ b/artfynd/A 13155-2025 artfynd.xlsx
@@ -1169,7 +1169,7 @@
         <v>133842236</v>
       </c>
       <c r="B6" t="n">
-        <v>58250</v>
+        <v>58260</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
